--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ninon est à l'école. La maîtresse parle. Ninon aime écouter. La maîtresse dit : on range les feutres. Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote. Il dit : c'est un secret. Garde ça pour toi. Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison. Elle dit : papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Papa l'écoute. Papa dit : tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
+          <t>Ninon est à l'école. La maîtresse parle. Ninon aime écouter. On range les feutres. Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote. C'est un secret. Garde ça pour toi. Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Papa l'écoute. Tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon est à l'école. La maîtresse parle. Ninon aime écouter.
+maitresse|On range les feutres.
+narrateur|Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote.
+narrateur|C'est un secret. Garde ça pour toi.
+narrateur|Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison.
+narrateur|Papa, j'ai eu un malaise.
+narrateur|Un camarade a parlé d'un secret. Papa l'écoute.
+papa|Tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ninon boit un verre d'eau. Papa lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 papa|Tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Ninon a un malaise. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Ninon boit un verre d'eau. Papa lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ninon écoute, puis elle raconte</t>
+          <t>La craie d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>De la craie blanche poudre le pas de la porte. Amir souffle dessus. À l'école il écoute et range son feutre. Un chuchotement serre son ventre. Le soir, il raconte à papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ninon est à l'école. La maîtresse parle. Ninon aime écouter. On range les feutres. Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote. C'est un secret. Garde ça pour toi. Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Papa l'écoute. Tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
+          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Bravo. Tes pieds restent sur la pierre. Tu as tes feutres dans la boîte ? Oui, maman. Clic. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir aime écouter. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Tu as bien écouté. Plus tard, un camarade s'approche. Il parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Le soir, la craie est encore sur la pierre. Te voilà. Le tapis est rentré. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Tu as bien fait de raconter. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman. Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,17 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ninon est à l'école. La maîtresse parle. Ninon aime écouter.
-maitresse|On range les feutres.
-narrateur|Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote.
-narrateur|C'est un secret. Garde ça pour toi.
-narrateur|Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison.
-narrateur|Papa, j'ai eu un malaise.
-narrateur|Un camarade a parlé d'un secret. Papa l'écoute.
-papa|Tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|De la craie blanche poudre le pas de la porte.
+narrateur|Un platane du village bouge, tout lent.
+narrateur|Une feuille tourne, puis s'arrête.
+narrateur|Papa secoue le tapis. Un nuage gris s'envole.
+narrateur|Maman ferme la boîte des feutres, clic.
+narrateur|Ça sent le bois du tapis et l'air du matin.
+papa|Il reste de la marelle, d'hier.
+maman|La craie a fait un petit chemin blanc.
+narrateur|En ce moment, Amir souffle sur la craie.
+narrateur|La poudre vole, puis retombe.
+enfant-m|Elle pique le nez, papa.
+papa|Souffle à côté. Bravo. Tes pieds restent sur la pierre.
+maman|Tu as tes feutres dans la boîte ?
+enfant-m|Oui, maman. Clic.
+papa|On y va. Tu dis au revoir à maman.
+enfant-m|Au revoir, maman.
+maman|Je t'écoute ce soir, Amir.
+narrateur|L'école sent les feutres et le papier.
+maitresse|Bonjour. On range les feutres.
+enfant-m|Bonjour, maîtresse.
+narrateur|Amir aime écouter.
+narrateur|Il range son feutre vert, le bouchon bien fermé.
+narrateur|Le vert sent un peu fort, tout près.
+maitresse|Merci, Amir. Tu as bien écouté.
+narrateur|Plus tard, un camarade s'approche.
+narrateur|Il parle tout bas, d'un secret.
+narrateur|Amir sent un malaise. Son ventre se serre.
+narrateur|Il repose les mains sur ses genoux.
+narrateur|Le soir, la craie est encore sur la pierre.
+papa|Te voilà. Le tapis est rentré.
+enfant-m|Papa, j'ai eu un malaise.
+enfant-m|Un camarade a parlé d'un secret.
+papa|Tu as bien fait de raconter.
+maman|On aime écouter la maîtresse.
+papa|Si tu as un malaise, tu viens raconter à papa ou maman.
+maman|Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>porte,pas</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ninon a un malaise. Que fait-elle ?</t>
+          <t>Amir a un malaise. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1547,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ninon a un malaise. Que fait-elle ?</t>
+          <t>narrateur|Amir a un malaise.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1576,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là.</t>
+          <t>Amir a écouté la maîtresse. Il a raconté son malaise à la maison. Tu es venu nous le dire. Bravo, Amir. C'est du bon travail. Tu as fini de ranger ton cartable ? Oui, papa. Une trace de craie reste sur la pierre. Le vent la prend.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1716,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là.</t>
+          <t>narrateur|Amir a écouté la maîtresse.
+narrateur|Il a raconté son malaise à la maison.
+papa|Tu es venu nous le dire. Bravo, Amir.
+maman|C'est du bon travail.
+papa|Tu as fini de ranger ton cartable ?
+enfant-m|Oui, papa.
+narrateur|Une trace de craie reste sur la pierre. Le vent la prend.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1750,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ninon boit un verre d'eau. Papa lui tient la main.</t>
+          <t>Amir boit un verre d'eau. Papa lui tient la main. Le platane bouge encore, tout lent. Tu as vu la feuille qui tourne ? Oui. Elle est jaune. On reste encore un peu sur le pas de la porte ? Oui. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1890,13 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ninon boit un verre d'eau. Papa lui tient la main.</t>
+          <t>narrateur|Amir boit un verre d'eau.
+narrateur|Papa lui tient la main.
+maman|Le platane bouge encore, tout lent.
+papa|Tu as vu la feuille qui tourne ?
+enfant-m|Oui. Elle est jaune.
+maman|On reste encore un peu sur le pas de la porte ?
+enfant-m|Oui. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1924,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai écouté. Puis j'ai raconté. Bravo. Tu as fait du bon travail. La craie a volé. On t'a écouté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2064,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai écouté. Puis j'ai raconté.
+papa|Bravo. Tu as fait du bon travail.
+maman|La craie a volé. On t'a écouté.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2127,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Bravo. Tes pieds restent sur la pierre. Tu as tes feutres dans la boîte ? Oui, maman. Clic. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir aime écouter. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Tu as bien écouté. Plus tard, un camarade s'approche. Il parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Le soir, la craie est encore sur la pierre. Te voilà. Le tapis est rentré. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Tu as bien fait de raconter. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman. Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
+          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Bravo. Tes pieds restent sur la pierre. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir aime écouter. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Tu as bien écouté. Plus tard, un camarade s'approche. Il parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Le soir, la craie est encore sur la pierre. Te voilà. Le tapis est rentré. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Tu as bien fait de raconter. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman. Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1327,7 +1327,8 @@
           <t>narrateur|De la craie blanche poudre le pas de la porte.
 narrateur|Un platane du village bouge, tout lent.
 narrateur|Une feuille tourne, puis s'arrête.
-narrateur|Papa secoue le tapis. Un nuage gris s'envole.
+narrateur|Papa secoue le tapis.
+narrateur|Un nuage gris s'envole.
 narrateur|Maman ferme la boîte des feutres, clic.
 narrateur|Ça sent le bois du tapis et l'air du matin.
 papa|Il reste de la marelle, d'hier.
@@ -1335,31 +1336,45 @@
 narrateur|En ce moment, Amir souffle sur la craie.
 narrateur|La poudre vole, puis retombe.
 enfant-m|Elle pique le nez, papa.
-papa|Souffle à côté. Bravo. Tes pieds restent sur la pierre.
+papa|Souffle à côté.
+papa|Bravo.
+papa|Tes pieds restent sur la pierre.
 maman|Tu as tes feutres dans la boîte ?
-enfant-m|Oui, maman. Clic.
-papa|On y va. Tu dis au revoir à maman.
+enfant-m|Oui, maman.
+enfant-m|Clic.
+papa|Le platane a encore des feuilles jaunes, tu vois ?
+enfant-m|Oui.
+enfant-m|Une est tombée.
+maman|On la laisse.
+maman|Elle est jolie par terre.
+papa|On y va.
+papa|Tu dis au revoir à maman.
 enfant-m|Au revoir, maman.
 maman|Je t'écoute ce soir, Amir.
 narrateur|L'école sent les feutres et le papier.
-maitresse|Bonjour. On range les feutres.
+maitresse|Bonjour.
+maitresse|On range les feutres.
 enfant-m|Bonjour, maîtresse.
 narrateur|Amir aime écouter.
 narrateur|Il range son feutre vert, le bouchon bien fermé.
 narrateur|Le vert sent un peu fort, tout près.
-maitresse|Merci, Amir. Tu as bien écouté.
+maitresse|Merci, Amir.
+maitresse|Tu as bien écouté.
 narrateur|Plus tard, un camarade s'approche.
 narrateur|Il parle tout bas, d'un secret.
-narrateur|Amir sent un malaise. Son ventre se serre.
+narrateur|Amir sent un malaise.
+narrateur|Son ventre se serre.
 narrateur|Il repose les mains sur ses genoux.
 narrateur|Le soir, la craie est encore sur la pierre.
-papa|Te voilà. Le tapis est rentré.
+papa|Te voilà.
+papa|Le tapis est rentré.
 enfant-m|Papa, j'ai eu un malaise.
 enfant-m|Un camarade a parlé d'un secret.
 papa|Tu as bien fait de raconter.
 maman|On aime écouter la maîtresse.
 papa|Si tu as un malaise, tu viens raconter à papa ou maman.
-maman|Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
+maman|Tu as rangé ton feutre, puis tu as raconté.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1718,11 +1733,13 @@
         <is>
           <t>narrateur|Amir a écouté la maîtresse.
 narrateur|Il a raconté son malaise à la maison.
-papa|Tu es venu nous le dire. Bravo, Amir.
+papa|Tu es venu nous le dire.
+papa|Bravo, Amir.
 maman|C'est du bon travail.
 papa|Tu as fini de ranger ton cartable ?
 enfant-m|Oui, papa.
-narrateur|Une trace de craie reste sur la pierre. Le vent la prend.</t>
+narrateur|Une trace de craie reste sur la pierre.
+narrateur|Le vent la prend.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1894,9 +1911,12 @@
 narrateur|Papa lui tient la main.
 maman|Le platane bouge encore, tout lent.
 papa|Tu as vu la feuille qui tourne ?
-enfant-m|Oui. Elle est jaune.
+enfant-m|Oui.
+enfant-m|Elle est jaune.
 maman|On reste encore un peu sur le pas de la porte ?
-enfant-m|Oui. Merci, maman. Merci, papa.</t>
+enfant-m|Oui.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -2064,9 +2084,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai écouté. Puis j'ai raconté.
-papa|Bravo. Tu as fait du bon travail.
-maman|La craie a volé. On t'a écouté.
+          <t>enfant-m|J'ai écouté.
+enfant-m|Puis j'ai raconté.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+maman|La craie a volé.
+maman|On t'a écouté.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2089,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2132,6 +2155,41 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis maison</t>
+          <t>pas de la porte, platane du village, pierre du soir</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ninon, papa, maîtresse</t>
+          <t>Amir, papa, maman, maîtresse</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre le pas de la porte. Amir souffle dessus. À l'école il écoute et range son feutre. Un chuchotement serre son ventre. Le soir, il raconte à papa et maman.</t>
+          <t>Amir souffle la poudre de marelle, puis ferme son feutre vert à l'école. Un chuchotement serre son ventre. Le soir, il raconte, et la feuille jaune reste sous le platane.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Bravo. Tes pieds restent sur la pierre. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir aime écouter. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Tu as bien écouté. Plus tard, un camarade s'approche. Il parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Le soir, la craie est encore sur la pierre. Te voilà. Le tapis est rentré. Papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Tu as bien fait de raconter. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman. Tu as rangé ton feutre, puis tu as raconté. Bravo.</t>
+          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Amir souffle sur le côté. La poudre part vers le platane. Tes pieds restent sur la pierre. Je veux emporter le feutre vert. Pour la marelle, plus tard. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir écoute. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Plus tard, quelqu'un s'approche. Une voix parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la craie est encore sur la pierre. La porte s'ouvre. Te voilà. Le tapis est rentré. Amir regarde le chemin blanc. La feuille jaune est encore là. Le ventre est encore serré.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ninon est à l'école. La maîtresse parle. Ninon aime &lt;emphasis level="moderate"&gt;écouter&lt;/emphasis&gt;. La maîtresse dit : on range les feutres. Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote. Il dit : c'est un secret. Garde ça pour toi. Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison. Elle dit : papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Papa l'écoute. Papa dit : tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Amir souffle sur le côté. La poudre part vers le platane. Tes pieds restent sur la pierre. Je veux emporter le feutre vert. Pour la marelle, plus tard. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir écoute. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Plus tard, quelqu'un s'approche. Une voix parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la craie est encore sur la pierre. La porte s'ouvre. Te voilà. Le tapis est rentré. Amir regarde le chemin blanc. La feuille jaune est encore là. Le ventre est encore serré.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1337,8 +1337,11 @@
 narrateur|La poudre vole, puis retombe.
 enfant-m|Elle pique le nez, papa.
 papa|Souffle à côté.
-papa|Bravo.
+narrateur|Amir souffle sur le côté.
+narrateur|La poudre part vers le platane.
 papa|Tes pieds restent sur la pierre.
+enfant-m|Je veux emporter le feutre vert.
+enfant-m|Pour la marelle, plus tard.
 maman|Tu as tes feutres dans la boîte ?
 enfant-m|Oui, maman.
 enfant-m|Clic.
@@ -1355,26 +1358,23 @@
 maitresse|Bonjour.
 maitresse|On range les feutres.
 enfant-m|Bonjour, maîtresse.
-narrateur|Amir aime écouter.
+narrateur|Amir écoute.
 narrateur|Il range son feutre vert, le bouchon bien fermé.
 narrateur|Le vert sent un peu fort, tout près.
 maitresse|Merci, Amir.
-maitresse|Tu as bien écouté.
-narrateur|Plus tard, un camarade s'approche.
-narrateur|Il parle tout bas, d'un secret.
+narrateur|Plus tard, quelqu'un s'approche.
+narrateur|Une voix parle tout bas, d'un secret.
 narrateur|Amir sent un malaise.
 narrateur|Son ventre se serre.
 narrateur|Il repose les mains sur ses genoux.
+narrateur|Il reste près de sa chaise.
 narrateur|Le soir, la craie est encore sur la pierre.
+narrateur|La porte s'ouvre.
 papa|Te voilà.
 papa|Le tapis est rentré.
-enfant-m|Papa, j'ai eu un malaise.
-enfant-m|Un camarade a parlé d'un secret.
-papa|Tu as bien fait de raconter.
-maman|On aime écouter la maîtresse.
-papa|Si tu as un malaise, tu viens raconter à papa ou maman.
-maman|Tu as rangé ton feutre, puis tu as raconté.
-maman|Bravo.</t>
+narrateur|Amir regarde le chemin blanc.
+narrateur|La feuille jaune est encore là.
+narrateur|Le ventre est encore serré.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ninon a un malaise. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a un malaise. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>raconter | elle raconte | à papa | à la maison | écouter</t>
+          <t>raconter | il raconte | à papa | à la maison | écouter</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle raconte à papa. Que fait Ninon ?</t>
+          <t>Il raconte à papa. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1490,7 +1490,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1566,7 +1566,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1591,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a écouté la maîtresse. Il a raconté son malaise à la maison. Tu es venu nous le dire. Bravo, Amir. C'est du bon travail. Tu as fini de ranger ton cartable ? Oui, papa. Une trace de craie reste sur la pierre. Le vent la prend.</t>
+          <t>Papa. J'ai eu un malaise. Quelqu'un a parlé d'un secret. On t'écoute. Viens sur la pierre, près de nous. Amir parle. Papa écoute. Maman écoute. Tu as bien fait de raconter. À l'école, on écoute la maîtresse. Si tu as un malaise, tu viens le dire. Le ventre d'Amir se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa. J'ai eu un malaise. Quelqu'un a parlé d'un secret. On t'écoute. Viens sur la pierre, près de nous. Amir parle. Papa écoute. Maman écoute. Tu as bien fait de raconter. À l'école, on écoute la maîtresse. Si tu as un malaise, tu viens le dire. Le ventre d'Amir se desserre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1731,18 +1730,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amir a écouté la maîtresse.
-narrateur|Il a raconté son malaise à la maison.
-papa|Tu es venu nous le dire.
-papa|Bravo, Amir.
-maman|C'est du bon travail.
-papa|Tu as fini de ranger ton cartable ?
-enfant-m|Oui, papa.
-narrateur|Une trace de craie reste sur la pierre.
-narrateur|Le vent la prend.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-m|Papa.
+enfant-m|J'ai eu un malaise.
+enfant-m|Quelqu'un a parlé d'un secret.
+papa|On t'écoute.
+maman|Viens sur la pierre, près de nous.
+narrateur|Amir parle.
+narrateur|Papa écoute.
+narrateur|Maman écoute.
+papa|Tu as bien fait de raconter.
+maman|À l'école, on écoute la maîtresse.
+papa|Si tu as un malaise, tu viens le dire.
+narrateur|Le ventre d'Amir se desserre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1767,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amir boit un verre d'eau. Papa lui tient la main. Le platane bouge encore, tout lent. Tu as vu la feuille qui tourne ? Oui. Elle est jaune. On reste encore un peu sur le pas de la porte ? Oui. Merci, maman. Merci, papa.</t>
+          <t>Maman verse un peu d'eau dans un verre. L'eau fait un petit bruit clair. Tu veux un peu d'eau ? Oui. Merci, maman. Amir boit une gorgée. Tu as tes pieds sur la pierre ? Oui, papa. Amir souffle encore, à côté de la craie. Un peu de poudre s'envole. Elle ne pique plus. La feuille jaune est toujours là. On la laisse. On reste encore un peu ensemble ? Oui, papa. Le platane bouge, tout lent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ninon boit un verre d'eau. Papa lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman verse un peu d'eau dans un verre. L'eau fait un petit bruit clair. Tu veux un peu d'eau ? Oui. Merci, maman. Amir boit une gorgée. Tu as tes pieds sur la pierre ? Oui, papa. Amir souffle encore, à côté de la craie. Un peu de poudre s'envole. Elle ne pique plus. La feuille jaune est toujours là. On la laisse. On reste encore un peu ensemble ? Oui, papa. Le platane bouge, tout lent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1835,7 +1836,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1907,19 +1908,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amir boit un verre d'eau.
-narrateur|Papa lui tient la main.
-maman|Le platane bouge encore, tout lent.
-papa|Tu as vu la feuille qui tourne ?
-enfant-m|Oui.
-enfant-m|Elle est jaune.
-maman|On reste encore un peu sur le pas de la porte ?
+          <t>narrateur|Maman verse un peu d'eau dans un verre.
+narrateur|L'eau fait un petit bruit clair.
+maman|Tu veux un peu d'eau ?
 enfant-m|Oui.
 enfant-m|Merci, maman.
-enfant-m|Merci, papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|Amir boit une gorgée.
+papa|Tu as tes pieds sur la pierre ?
+enfant-m|Oui, papa.
+narrateur|Amir souffle encore, à côté de la craie.
+narrateur|Un peu de poudre s'envole.
+enfant-m|Elle ne pique plus.
+maman|La feuille jaune est toujours là.
+enfant-m|On la laisse.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui, papa.
+narrateur|Le platane bouge, tout lent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1944,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai écouté. Puis j'ai raconté. Bravo. Tu as fait du bon travail. La craie a volé. On t'a écouté. L'histoire est finie.</t>
+          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2012,7 +2018,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2084,16 +2090,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai écouté.
-enfant-m|Puis j'ai raconté.
-papa|Bravo.
-papa|Tu as fait du bon travail.
-maman|La craie a volé.
-maman|On t'a écouté.
+          <t>narrateur|Le chemin de craie s'efface un peu.
+narrateur|La feuille jaune reste sous le platane.
+papa|On t'a écouté, Amir.
+maman|Tu as rangé ton feutre, puis tu as raconté.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2112,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2192,6 +2195,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -1950,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté. L'histoire est finie.</t>
+          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté. L'histoire est finie.</t>
+          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,8 +2093,7 @@
           <t>narrateur|Le chemin de craie s'efface un peu.
 narrateur|La feuille jaune reste sous le platane.
 papa|On t'a écouté, Amir.
-maman|Tu as rangé ton feutre, puis tu as raconté.
-narrateur|L'histoire est finie.</t>
+maman|Tu as rangé ton feutre, puis tu as raconté.</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2200,6 +2199,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-COL.ECO.001-07.xlsx
+++ b/stories/arbres/ATOM-COL.ECO.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pas de la porte, platane du village, pierre du soir</t>
+          <t>école puis maison, pas de la porte, platane du village</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amir, papa, maman, maîtresse</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir souffle la poudre de marelle, puis ferme son feutre vert à l'école. Un chuchotement serre son ventre. Le soir, il raconte, et la feuille jaune reste sous le platane.</t>
+          <t>La craie d'hier poudre le pas de la porte. Sur la pierre, un éclat de craie brille. Amir veut la garder, maintenant. Il la saisit trop vite : elle casse, la poudre pique. À l'école, une voix parle d'un secret. Il veut le dire tout de suite : les mots se perdent. Il refuse de foncer, raconte le soir. Merci vécu. Sur la pierre, l'éclat de craie tient.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Amir souffle sur le côté. La poudre part vers le platane. Tes pieds restent sur la pierre. Je veux emporter le feutre vert. Pour la marelle, plus tard. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir écoute. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Plus tard, quelqu'un s'approche. Une voix parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la craie est encore sur la pierre. La porte s'ouvre. Te voilà. Le tapis est rentré. Amir regarde le chemin blanc. La feuille jaune est encore là. Le ventre est encore serré.</t>
+          <t>La craie d'hier poudre le pas de la porte. Le platane du village bouge ses branches. Une feuille jaune tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. Sur la pierre, un éclat de craie brille. Il est petit, papa. C'est la craie d'hier. Je la prends, maintenant ! En ce moment, Amir saisit la craie. La craie casse entre ses doigts. La poudre vole, puis retombe. Elle pique le nez, papa ! L'éclat de craie tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne veut pas ! Tu souffles à côté ? Papa s'accroupit à la même hauteur. Amir souffle trop fort, trop vite. La poudre lui revient au visage. Oh. Ses épaules tombent un peu. Tes pieds sont sur la pierre ? Oui, papa. Tes feutres sont dans la boîte ? Oui, maman. Clic. Tu vois la feuille jaune ? Oui. Elle est tombée. On la laisse par terre ? Oui, elle est jolie. On y va ? On y va. Au revoir, maman. Au revoir, Amir. Dehors, le chemin sent la pierre froide. Une feuille jaune tape le platane. L'école sent les feutres et le papier. La maîtresse parle près du tableau. Bonjour. Bonjour, maîtresse. Amir pose le feutre vert, bouchon fermé. Le vert sent un peu fort, tout près. Une poussière de tableau flotte dans l'air. Plus tard, une voix s'approche. Elle parle bas, d'un secret. Amir sent un malaise. Son ventre se serre. Je le dis, maintenant ! Ses mots se cognent à ceux de la classe. Personne ne tourne la tête. Amir referme la bouche. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la porte s'ouvre. Ça sent le tapis et la pierre. Te voilà, Amir. Le tapis est rentré. La craie attend sur la pierre. La feuille jaune est là. Le ventre est serré, tout petit. Amir regarde papa. Il ouvre la bouche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>De la craie blanche poudre le pas de la porte. Un platane du village bouge, tout lent. Une feuille tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. En ce moment, Amir souffle sur la craie. La poudre vole, puis retombe. Elle pique le nez, papa. Souffle à côté. Amir souffle sur le côté. La poudre part vers le platane. Tes pieds restent sur la pierre. Je veux emporter le feutre vert. Pour la marelle, plus tard. Tu as tes feutres dans la boîte ? Oui, maman. Clic. Le platane a encore des feuilles jaunes, tu vois ? Oui. Une est tombée. On la laisse. Elle est jolie par terre. On y va. Tu dis au revoir à maman. Au revoir, maman. Je t'écoute ce soir, Amir. L'école sent les feutres et le papier. Bonjour. On range les feutres. Bonjour, maîtresse. Amir écoute. Il range son feutre vert, le bouchon bien fermé. Le vert sent un peu fort, tout près. Merci, Amir. Plus tard, quelqu'un s'approche. Une voix parle tout bas, d'un secret. Amir sent un malaise. Son ventre se serre. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la craie est encore sur la pierre. La porte s'ouvre. Te voilà. Le tapis est rentré. Amir regarde le chemin blanc. La feuille jaune est encore là. Le ventre est encore serré.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La craie d'hier poudre le pas de la porte. Le platane du village bouge ses branches. Une feuille jaune tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. Sur la pierre, un &lt;emphasis level="moderate"&gt;éclat de craie&lt;/emphasis&gt; brille. Il est petit, papa. C'est la craie d'hier. Je la prends, maintenant ! En ce moment, Amir saisit la craie. La craie casse entre ses doigts. La poudre vole, puis retombe. Elle pique le nez, papa ! L'éclat de craie tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne veut pas ! Tu souffles à côté ? Papa s'accroupit à la même hauteur. Amir souffle trop fort, trop vite. La poudre lui revient au visage. Oh. Ses épaules tombent un peu. Tes pieds sont sur la pierre ? Oui, papa. Tes feutres sont dans la boîte ? Oui, maman. Clic. Tu vois la feuille jaune ? Oui. Elle est tombée. On la laisse par terre ? Oui, elle est jolie. On y va ? On y va. Au revoir, maman. Au revoir, Amir. Dehors, le chemin sent la pierre froide. Une feuille jaune tape le platane. L'école sent les feutres et le papier. La maîtresse parle près du tableau. Bonjour. Bonjour, maîtresse. Amir pose le feutre vert, bouchon fermé. Le vert sent un peu fort, tout près. Une poussière de tableau flotte dans l'air. Plus tard, une voix s'approche. Elle parle bas, d'un secret. Amir sent un malaise. Son ventre se serre. Je le dis, maintenant ! Ses mots se cognent à ceux de la classe. Personne ne tourne la tête. Amir referme la bouche. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la porte s'ouvre. Ça sent le tapis et la pierre. Te voilà, Amir. Le tapis est rentré. La craie attend sur la pierre. La feuille jaune est là. Le ventre est serré, tout petit. Amir regarde papa. Il ouvre la bouche.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Ninon est à l'école. La maîtresse parle. Ninon aime &lt;emphasis&gt;écouter&lt;/emphasis&gt;. La maîtresse dit : on range les feutres. Ninon range son feutre. Elle écoute bien. Plus tard, un camarade chuchote. Il dit : c'est un secret. Garde ça pour toi. Ninon sent un malaise. Son ventre est serré. Le soir, papa l'attend. Ninon vient raconter à la maison. Elle dit : papa, j'ai eu un malaise. Un camarade a parlé d'un secret. Papa l'écoute. Papa dit : tu as bien fait. On aime écouter la maîtresse. Si tu as un malaise, tu viens raconter à papa ou maman. [pause]</t>
+          <t>La craie d'hier poudre le pas de la porte. Le platane du village bouge ses branches. Une feuille jaune tourne, puis s'arrête. Papa secoue le tapis. Un nuage gris s'envole. Maman ferme la boîte des feutres, clic. Ça sent le bois du tapis et l'air du matin. Il reste de la marelle, d'hier. La craie a fait un petit chemin blanc. Sur la pierre, un &lt;emphasis&gt;éclat de craie&lt;/emphasis&gt; brille. Il est petit, papa. C'est la craie d'hier. Je la prends, maintenant ! En ce moment, Amir saisit la craie. La craie casse entre ses doigts. La poudre vole, puis retombe. Elle pique le nez, papa ! L'éclat de craie tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ça ne veut pas ! Tu souffles à côté ? Papa s'accroupit à la même hauteur. Amir souffle trop fort, trop vite. La poudre lui revient au visage. Oh. Ses épaules tombent un peu. Tes pieds sont sur la pierre ? Oui, papa. Tes feutres sont dans la boîte ? Oui, maman. Clic. Tu vois la feuille jaune ? Oui. Elle est tombée. On la laisse par terre ? Oui, elle est jolie. On y va ? On y va. Au revoir, maman. Au revoir, Amir. Dehors, le chemin sent la pierre froide. Une feuille jaune tape le platane. L'école sent les feutres et le papier. La maîtresse parle près du tableau. Bonjour. Bonjour, maîtresse. Amir pose le feutre vert, bouchon fermé. Le vert sent un peu fort, tout près. Une poussière de tableau flotte dans l'air. Plus tard, une voix s'approche. Elle parle bas, d'un secret. Amir sent un malaise. Son ventre se serre. Je le dis, maintenant ! Ses mots se cognent à ceux de la classe. Personne ne tourne la tête. Amir referme la bouche. Il repose les mains sur ses genoux. Il reste près de sa chaise. Le soir, la porte s'ouvre. Ça sent le tapis et la pierre. Te voilà, Amir. Le tapis est rentré. La craie attend sur la pierre. La feuille jaune est là. Le ventre est serré, tout petit. Amir regarde papa. Il ouvre la bouche. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>écouter</t>
+          <t>éclat de craie</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,65 +1321,87 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis malaise; intensite=2; destinataire=enfant; sous_texte=il_veut_la_craie_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|De la craie blanche poudre le pas de la porte.
-narrateur|Un platane du village bouge, tout lent.
-narrateur|Une feuille tourne, puis s'arrête.
+          <t>narrateur|La craie d'hier poudre le pas de la porte.
+narrateur|Le platane du village bouge ses branches.
+narrateur|Une feuille jaune tourne, puis s'arrête.
 narrateur|Papa secoue le tapis.
 narrateur|Un nuage gris s'envole.
 narrateur|Maman ferme la boîte des feutres, clic.
 narrateur|Ça sent le bois du tapis et l'air du matin.
 papa|Il reste de la marelle, d'hier.
 maman|La craie a fait un petit chemin blanc.
-narrateur|En ce moment, Amir souffle sur la craie.
+narrateur|Sur la pierre, un éclat de craie brille.
+enfant-m|Il est petit, papa.
+papa|C'est la craie d'hier.
+enfant-m|Je la prends, maintenant !
+narrateur|En ce moment, Amir saisit la craie.
+narrateur|La craie casse entre ses doigts.
 narrateur|La poudre vole, puis retombe.
-enfant-m|Elle pique le nez, papa.
-papa|Souffle à côté.
-narrateur|Amir souffle sur le côté.
-narrateur|La poudre part vers le platane.
-papa|Tes pieds restent sur la pierre.
-enfant-m|Je veux emporter le feutre vert.
-enfant-m|Pour la marelle, plus tard.
-maman|Tu as tes feutres dans la boîte ?
+enfant-m|Elle pique le nez, papa !
+narrateur|L'éclat de craie tremble, puis tient.
+narrateur|Le sourire d'Amir disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+enfant-m|Ça ne veut pas !
+papa|Tu souffles à côté ?
+narrateur|Papa s'accroupit à la même hauteur.
+narrateur|Amir souffle trop fort, trop vite.
+narrateur|La poudre lui revient au visage.
+enfant-m|Oh.
+narrateur|Ses épaules tombent un peu.
+papa|Tes pieds sont sur la pierre ?
+enfant-m|Oui, papa.
+maman|Tes feutres sont dans la boîte ?
 enfant-m|Oui, maman.
 enfant-m|Clic.
-papa|Le platane a encore des feuilles jaunes, tu vois ?
+papa|Tu vois la feuille jaune ?
 enfant-m|Oui.
-enfant-m|Une est tombée.
-maman|On la laisse.
-maman|Elle est jolie par terre.
-papa|On y va.
-papa|Tu dis au revoir à maman.
+enfant-m|Elle est tombée.
+maman|On la laisse par terre ?
+enfant-m|Oui, elle est jolie.
+papa|On y va ?
+enfant-m|On y va.
 enfant-m|Au revoir, maman.
-maman|Je t'écoute ce soir, Amir.
+maman|Au revoir, Amir.
+narrateur|Dehors, le chemin sent la pierre froide.
+narrateur|Une feuille jaune tape le platane.
 narrateur|L'école sent les feutres et le papier.
+narrateur|La maîtresse parle près du tableau.
 maitresse|Bonjour.
-maitresse|On range les feutres.
 enfant-m|Bonjour, maîtresse.
-narrateur|Amir écoute.
-narrateur|Il range son feutre vert, le bouchon bien fermé.
+narrateur|Amir pose le feutre vert, bouchon fermé.
 narrateur|Le vert sent un peu fort, tout près.
-maitresse|Merci, Amir.
-narrateur|Plus tard, quelqu'un s'approche.
-narrateur|Une voix parle tout bas, d'un secret.
+narrateur|Une poussière de tableau flotte dans l'air.
+narrateur|Plus tard, une voix s'approche.
+narrateur|Elle parle bas, d'un secret.
 narrateur|Amir sent un malaise.
 narrateur|Son ventre se serre.
+enfant-m|Je le dis, maintenant !
+narrateur|Ses mots se cognent à ceux de la classe.
+narrateur|Personne ne tourne la tête.
+narrateur|Amir referme la bouche.
 narrateur|Il repose les mains sur ses genoux.
 narrateur|Il reste près de sa chaise.
-narrateur|Le soir, la craie est encore sur la pierre.
-narrateur|La porte s'ouvre.
-papa|Te voilà.
+narrateur|Le soir, la porte s'ouvre.
+narrateur|Ça sent le tapis et la pierre.
+papa|Te voilà, Amir.
 papa|Le tapis est rentré.
-narrateur|Amir regarde le chemin blanc.
-narrateur|La feuille jaune est encore là.
-narrateur|Le ventre est encore serré.</t>
+narrateur|La craie attend sur la pierre.
+narrateur|La feuille jaune est là.
+narrateur|Le ventre est serré, tout petit.
+narrateur|Amir regarde papa.
+narrateur|Il ouvre la bouche.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>porte,pas</t>
+          <t>craie,tapis</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1433,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Amir a un malaise. Que fait-il ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Amir a un &lt;emphasis level="moderate"&gt;malaise&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Ninon a un malaise. Que fait-elle ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Amir a un &lt;emphasis&gt;malaise&lt;/emphasis&gt;. Que fait-il ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1426,7 +1448,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>raconter | il raconte | à papa | à la maison | écouter</t>
+          <t>raconter | il raconte | à papa | à la maison | il dit | le secret | il parle | papa maman</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1441,7 +1463,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il raconte à papa. Que fait Amir ?</t>
+          <t>Amir a un malaise à la maison. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1479,7 +1501,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1490,7 +1512,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,34 +1527,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>malaise</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1547,17 +1573,17 @@
         <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=il_raconte_a_la_maison; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1590,17 +1616,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Papa. J'ai eu un malaise. Quelqu'un a parlé d'un secret. On t'écoute. Viens sur la pierre, près de nous. Amir parle. Papa écoute. Maman écoute. Tu as bien fait de raconter. À l'école, on écoute la maîtresse. Si tu as un malaise, tu viens le dire. Le ventre d'Amir se desserre.</t>
+          <t>Amir ouvre la bouche trop vite. Papa, un secret. Papa n'a pas fini sa phrase. Le tapis est sec, Amir. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme la bouche. Il pose les mains à plat. Le pas de la porte est calme. Tes pieds sont sur la pierre ? Papa pose le tapis contre le mur. La feuille jaune est sous le platane. Maman n'a pas fini non plus. Amir attend que le silence arrive. Sur la pierre, l'éclat de craie brille. Il est là. Je peux te dire quelque chose ? Oui, nous t'écoutons. Une voix a parlé d'un secret. Mon ventre s'est serré. Merci, Amir. Papa a entendu toute la phrase. Tu veux un peu d'eau ? Oui, maman. Amir pose la main sur la pierre froide. Le ventre d'Amir se desserre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Papa. J'ai eu un malaise. Quelqu'un a parlé d'un secret. On t'écoute. Viens sur la pierre, près de nous. Amir parle. Papa écoute. Maman écoute. Tu as bien fait de raconter. À l'école, on écoute la maîtresse. Si tu as un malaise, tu viens le dire. Le ventre d'Amir se desserre.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir ouvre la bouche trop vite. Papa, un &lt;emphasis level="moderate"&gt;secret&lt;/emphasis&gt;. Papa n'a pas fini sa phrase. Le tapis est sec, Amir. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme la bouche. Il pose les mains à plat. Le pas de la porte est calme. Tes pieds sont sur la pierre ? Papa pose le tapis contre le mur. La feuille jaune est sous le platane. Maman n'a pas fini non plus. Amir attend que le silence arrive. Sur la pierre, l'éclat de craie brille. Il est là. Je peux te dire quelque chose ? Oui, nous t'écoutons. Une voix a parlé d'un secret. Mon ventre s'est serré. Merci, Amir. Papa a entendu toute la phrase. Tu veux un peu d'eau ? Oui, maman. Amir pose la main sur la pierre froide. Le ventre d'Amir se desserre.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Ninon a écouté la maîtresse. Elle a raconté son malaise à la maison. Papa est là. [pause]</t>
+          <t>Amir ouvre la bouche trop vite. Papa, un &lt;emphasis&gt;secret&lt;/emphasis&gt;. Papa n'a pas fini sa phrase. Le tapis est sec, Amir. Les deux voix se mélangent. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme la bouche. Il pose les mains à plat. Le pas de la porte est calme. Tes pieds sont sur la pierre ? Papa pose le tapis contre le mur. La feuille jaune est sous le platane. Maman n'a pas fini non plus. Amir attend que le silence arrive. Sur la pierre, l'éclat de craie brille. Il est là. Je peux te dire quelque chose ? Oui, nous t'écoutons. Une voix a parlé d'un secret. Mon ventre s'est serré. Merci, Amir. Papa a entendu toute la phrase. Tu veux un peu d'eau ? Oui, maman. Amir pose la main sur la pierre froide. Le ventre d'Amir se desserre. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1647,7 +1673,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1655,10 +1681,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,28 +1705,32 @@
       <c r="AG4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>secret</t>
+        </is>
+      </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1709,10 +1739,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1725,23 +1755,44 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_attend_puis_raconte; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>enfant-m|Papa.
-enfant-m|J'ai eu un malaise.
-enfant-m|Quelqu'un a parlé d'un secret.
-papa|On t'écoute.
-maman|Viens sur la pierre, près de nous.
-narrateur|Amir parle.
-narrateur|Papa écoute.
-narrateur|Maman écoute.
-papa|Tu as bien fait de raconter.
-maman|À l'école, on écoute la maîtresse.
-papa|Si tu as un malaise, tu viens le dire.
+          <t>narrateur|Amir ouvre la bouche trop vite.
+enfant-m|Papa, un secret.
+narrateur|Papa n'a pas fini sa phrase.
+papa|Le tapis est sec, Amir.
+narrateur|Les deux voix se mélangent.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Amir refuse de foncer.
+narrateur|Il referme la bouche.
+narrateur|Il pose les mains à plat.
+narrateur|Le pas de la porte est calme.
+papa|Tes pieds sont sur la pierre ?
+narrateur|Papa pose le tapis contre le mur.
+maman|La feuille jaune est sous le platane.
+narrateur|Maman n'a pas fini non plus.
+narrateur|Amir attend que le silence arrive.
+narrateur|Sur la pierre, l'éclat de craie brille.
+enfant-m|Il est là.
+enfant-m|Je peux te dire quelque chose ?
+maman|Oui, nous t'écoutons.
+enfant-m|Une voix a parlé d'un secret.
+enfant-m|Mon ventre s'est serré.
+papa|Merci, Amir.
+narrateur|Papa a entendu toute la phrase.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Amir pose la main sur la pierre froide.
 narrateur|Le ventre d'Amir se desserre.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>pierre,voix</t>
         </is>
       </c>
     </row>
@@ -1768,17 +1819,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman verse un peu d'eau dans un verre. L'eau fait un petit bruit clair. Tu veux un peu d'eau ? Oui. Merci, maman. Amir boit une gorgée. Tu as tes pieds sur la pierre ? Oui, papa. Amir souffle encore, à côté de la craie. Un peu de poudre s'envole. Elle ne pique plus. La feuille jaune est toujours là. On la laisse. On reste encore un peu ensemble ? Oui, papa. Le platane bouge, tout lent.</t>
+          <t>Maman verse de l'eau dans un verre. L'eau fait un petit bruit clair. C'est froid. Tes pieds sont au chaud ? Oui, sur la pierre. Amir boit une gorgée. Amir veut souffler la craie, tout de suite. Il souffle trop fort. La poudre lui pique les yeux. Oh. Amir s'arrête. Ses mains se ferment, puis s'ouvrent. Il refuse de foncer. Il écoute le platane, un instant. Il souffle à côté, plus léger. Un peu de poudre s'envole vers l'arbre. Elle ne pique plus. On laisse la feuille jaune ? Oui, par terre. On reste un peu ? Oui, papa. Le platane bouge ses branches.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman verse un peu d'eau dans un verre. L'eau fait un petit bruit clair. Tu veux un peu d'eau ? Oui. Merci, maman. Amir boit une gorgée. Tu as tes pieds sur la pierre ? Oui, papa. Amir souffle encore, à côté de la craie. Un peu de poudre s'envole. Elle ne pique plus. La feuille jaune est toujours là. On la laisse. On reste encore un peu ensemble ? Oui, papa. Le platane bouge, tout lent.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman verse de l'eau dans un verre. L'eau fait un petit bruit clair. C'est froid. Tes pieds sont au chaud ? Oui, sur la pierre. Amir boit une gorgée. Amir veut souffler la craie, tout de suite. Il souffle trop fort. La &lt;emphasis level="moderate"&gt;poudre&lt;/emphasis&gt; lui pique les yeux. Oh. Amir s'arrête. Ses mains se ferment, puis s'ouvrent. Il refuse de foncer. Il écoute le platane, un instant. Il souffle à côté, plus léger. Un peu de poudre s'envole vers l'arbre. Elle ne pique plus. On laisse la feuille jaune ? Oui, par terre. On reste un peu ? Oui, papa. Le platane bouge ses branches.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Ninon boit un verre d'eau. Papa lui tient la &lt;emphasis&gt;main&lt;/emphasis&gt;. [pause]</t>
+          <t>Maman verse de l'eau dans un verre. L'eau fait un petit bruit clair. C'est froid. Tes pieds sont au chaud ? Oui, sur la pierre. Amir boit une gorgée. Amir veut souffler la craie, tout de suite. Il souffle trop fort. La &lt;emphasis&gt;poudre&lt;/emphasis&gt; lui pique les yeux. Oh. Amir s'arrête. Ses mains se ferment, puis s'ouvrent. Il refuse de foncer. Il écoute le platane, un instant. Il souffle à côté, plus léger. Un peu de poudre s'envole vers l'arbre. Elle ne pique plus. On laisse la feuille jaune ? Oui, par terre. On reste un peu ? Oui, papa. Le platane bouge ses branches. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1825,7 +1876,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1833,10 +1884,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1859,30 +1910,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>poudre</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1891,10 +1942,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1905,25 +1956,40 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_souffler_trop_fort; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman verse un peu d'eau dans un verre.
+          <t>narrateur|Maman verse de l'eau dans un verre.
 narrateur|L'eau fait un petit bruit clair.
-maman|Tu veux un peu d'eau ?
-enfant-m|Oui.
-enfant-m|Merci, maman.
+enfant-m|C'est froid.
+papa|Tes pieds sont au chaud ?
+enfant-m|Oui, sur la pierre.
 narrateur|Amir boit une gorgée.
-papa|Tu as tes pieds sur la pierre ?
+narrateur|Amir veut souffler la craie, tout de suite.
+narrateur|Il souffle trop fort.
+narrateur|La poudre lui pique les yeux.
+enfant-m|Oh.
+narrateur|Amir s'arrête.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Il refuse de foncer.
+narrateur|Il écoute le platane, un instant.
+narrateur|Il souffle à côté, plus léger.
+narrateur|Un peu de poudre s'envole vers l'arbre.
+enfant-m|Elle ne pique plus.
+maman|On laisse la feuille jaune ?
+enfant-m|Oui, par terre.
+papa|On reste un peu ?
 enfant-m|Oui, papa.
-narrateur|Amir souffle encore, à côté de la craie.
-narrateur|Un peu de poudre s'envole.
-enfant-m|Elle ne pique plus.
-maman|La feuille jaune est toujours là.
-enfant-m|On la laisse.
-papa|On reste encore un peu ensemble ?
-enfant-m|Oui, papa.
-narrateur|Le platane bouge, tout lent.</t>
+narrateur|Le platane bouge ses branches.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>eau,poudre</t>
         </is>
       </c>
     </row>
@@ -1950,17 +2016,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté.</t>
+          <t>Ils restent sur le pas de la porte. La poudre blanche repose sur la pierre. Comme ce matin, papa ! Tu le vois, toi ? Oui, sur la pierre. On est bien, ici. Le tapis sent le bois, un peu. Amir glisse le pied, sans se presser. La craie repose contre la pierre. On le sent, maman. Tu le sens sur tes joues ? Oui, il est frais. Le platane repose contre le ciel. Une feuille jaune ne bouge plus. Elle est jolie par terre. On la laisse ? Oui. L'éclat de craie tient sur la pierre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le chemin de craie s'efface un peu. La feuille jaune reste sous le platane. On t'a écouté, Amir. Tu as rangé ton feutre, puis tu as raconté.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent sur le pas de la porte. La poudre blanche repose sur la pierre. Comme ce matin, papa ! Tu le vois, toi ? Oui, sur la pierre. On est bien, ici. Le tapis sent le bois, un peu. Amir glisse le pied, sans se presser. La craie repose contre la pierre. On le sent, maman. Tu le sens sur tes joues ? Oui, il est frais. Le platane repose contre le ciel. Une feuille jaune ne bouge plus. Elle est jolie par terre. On la laisse ? Oui. L'&lt;emphasis level="moderate"&gt;éclat de craie&lt;/emphasis&gt; tient sur la pierre.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent sur le pas de la porte. La poudre blanche repose sur la pierre. Comme ce matin, papa ! Tu le vois, toi ? Oui, sur la pierre. On est bien, ici. Le tapis sent le bois, un peu. Amir glisse le pied, sans se presser. La craie repose contre la pierre. On le sent, maman. Tu le sens sur tes joues ? Oui, il est frais. Le platane repose contre le ciel. Une feuille jaune ne bouge plus. Elle est jolie par terre. On la laisse ? Oui. L'&lt;emphasis&gt;éclat de craie&lt;/emphasis&gt; tient sur la pierre.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2007,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
@@ -2015,10 +2081,10 @@
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2027,12 +2093,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2041,17 +2107,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de craie</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2060,11 +2130,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2073,27 +2143,50 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_la_pierre; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Le chemin de craie s'efface un peu.
-narrateur|La feuille jaune reste sous le platane.
-papa|On t'a écouté, Amir.
-maman|Tu as rangé ton feutre, puis tu as raconté.</t>
+          <t>narrateur|Ils restent sur le pas de la porte.
+narrateur|La poudre blanche repose sur la pierre.
+enfant-m|Comme ce matin, papa !
+papa|Tu le vois, toi ?
+enfant-m|Oui, sur la pierre.
+maman|On est bien, ici.
+narrateur|Le tapis sent le bois, un peu.
+narrateur|Amir glisse le pied, sans se presser.
+narrateur|La craie repose contre la pierre.
+enfant-m|On le sent, maman.
+maman|Tu le sens sur tes joues ?
+enfant-m|Oui, il est frais.
+narrateur|Le platane repose contre le ciel.
+narrateur|Une feuille jaune ne bouge plus.
+enfant-m|Elle est jolie par terre.
+papa|On la laisse ?
+enfant-m|Oui.
+narrateur|L'éclat de craie tient sur la pierre.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>platane,pierre</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2206,6 +2299,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
